--- a/Assets/Data/Table/Item/RecipyData.xlsx
+++ b/Assets/Data/Table/Item/RecipyData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28019"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82F2C0B7-7B5A-4431-8573-963A910BAD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{040031A8-2689-4EDA-A8F3-A340804BE35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
   <si>
     <t>Id</t>
   </si>
@@ -90,6 +90,9 @@
     <t>OutputItem-4</t>
   </si>
   <si>
+    <t>OutputItemCount-4</t>
+  </si>
+  <si>
     <t>CraftingTime</t>
   </si>
   <si>
@@ -111,7 +114,7 @@
     <t>Text_Recipy_IronPlate_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_IronPlate.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_IronPlate.png</t>
   </si>
   <si>
     <t>Item_Iron</t>
@@ -129,10 +132,7 @@
     <t>Text_Recipy_IronPlate_Alternative_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_IronPlate_Alternative.png</t>
-  </si>
-  <si>
-    <t>1,5</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_IronPlate_Alternative.png</t>
   </si>
   <si>
     <t>Recipy_CopperPlate</t>
@@ -144,7 +144,7 @@
     <t>Text_Recipy_CopperPlate_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_CopperPlate.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_CopperPlate.png</t>
   </si>
   <si>
     <t>Item_Copper</t>
@@ -162,7 +162,7 @@
     <t>Text_Recipy_CopperPlate_Alternative_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_CopperPlate_Alternative.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_CopperPlate_Alternative.png</t>
   </si>
   <si>
     <t>Recipy_Crafter_T1</t>
@@ -174,7 +174,7 @@
     <t>Text_Recipy_Crafter_T1_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Crafter_T1.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Crafter_T1.png</t>
   </si>
   <si>
     <t>Recipy_Crater_T2</t>
@@ -186,7 +186,7 @@
     <t>Text_Recipy_Crater_T2_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Crater_T2.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Crater_T2.png</t>
   </si>
   <si>
     <t>Item_Crafter_T1</t>
@@ -201,7 +201,7 @@
     <t>Text_Recipy_Refinery_T1_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Refinery_T1.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Refinery_T1.png</t>
   </si>
   <si>
     <t>Recipy_Refinery_T2</t>
@@ -213,7 +213,7 @@
     <t>Text_Recipy_Refinery_T2_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Refinery_T2.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Refinery_T2.png</t>
   </si>
   <si>
     <t>Item_Refinery_T1</t>
@@ -228,7 +228,7 @@
     <t>Text_Recipy_Miner_T1_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Miner_T1.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Miner_T1.png</t>
   </si>
   <si>
     <t>Recipy_Miner_T2</t>
@@ -240,7 +240,7 @@
     <t>Text_Recipy_Miner_T2_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Miner_T2.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Miner_T2.png</t>
   </si>
   <si>
     <t>Item_Miner_T1</t>
@@ -255,7 +255,7 @@
     <t>Text_Recipy_Inserter_T1_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Inserter_T1.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Inserter_T1.png</t>
   </si>
   <si>
     <t>Recipy_Inserter_T2</t>
@@ -267,7 +267,7 @@
     <t>Text_Recipy_Inserter_T2_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Inserter_T2.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Inserter_T2.png</t>
   </si>
   <si>
     <t>Item_Inserter_T1</t>
@@ -282,7 +282,7 @@
     <t>Text_Recipy_Belt_T1_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Belt_T1.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Belt_T1.png</t>
   </si>
   <si>
     <t>Recipy_Belt_T2</t>
@@ -294,7 +294,7 @@
     <t>Text_Recipy_Belt_T2_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Belt_T2.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Belt_T2.png</t>
   </si>
   <si>
     <t>Item_Belt_T1</t>
@@ -309,7 +309,7 @@
     <t>Text_Recipy_Generator_T1_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Generator_T1.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Generator_T1.png</t>
   </si>
   <si>
     <t>Recipy_Generator_T2</t>
@@ -321,7 +321,7 @@
     <t>Text_Recipy_Generator_T2_Desc</t>
   </si>
   <si>
-    <t>\Resources\UI\Icon\Recipy\Icon_Recipy_Generator_T2.png</t>
+    <t>/Resources/UI/Icon/Recipy/Icon_Recipy_Generator_T2.png</t>
   </si>
   <si>
     <t>Item_Generator_T1</t>
@@ -879,6 +879,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="27.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
@@ -939,92 +962,92 @@
         <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="J2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="L2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="N2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="P2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="R2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="T2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -1036,7 +1059,7 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="7">
         <v>1</v>
@@ -1053,19 +1076,19 @@
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -1077,7 +1100,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N4" s="7">
         <v>2</v>
@@ -1088,8 +1111,8 @@
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
-      <c r="U4" s="5" t="s">
-        <v>33</v>
+      <c r="U4" s="5">
+        <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -1188,7 +1211,7 @@
         <v>47</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -1229,7 +1252,7 @@
         <v>51</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="7">
         <v>1</v>
@@ -1274,7 +1297,7 @@
         <v>56</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="7">
         <v>1</v>
@@ -1315,7 +1338,7 @@
         <v>60</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" s="7">
         <v>1</v>
@@ -1360,7 +1383,7 @@
         <v>65</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="7">
         <v>1</v>
@@ -1401,7 +1424,7 @@
         <v>69</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" s="7">
         <v>1</v>
@@ -1446,7 +1469,7 @@
         <v>74</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" s="7">
         <v>1</v>
@@ -1487,7 +1510,7 @@
         <v>78</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="7">
         <v>1</v>
@@ -1532,7 +1555,7 @@
         <v>83</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F15" s="7">
         <v>1</v>
@@ -1573,7 +1596,7 @@
         <v>87</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16" s="7">
         <v>1</v>
@@ -1618,7 +1641,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -1659,7 +1682,7 @@
         <v>96</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F18" s="9">
         <v>1</v>
